--- a/non_exclusive_zone_groups.xlsx
+++ b/non_exclusive_zone_groups.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hprpln.sharepoint.com/sites/Hyperplanners/Documents partages/2. Product/Consuelo/Templates secto/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victoria/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{5799324B-DAB1-B741-9F3B-C5928CF11A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E5889D8-1991-C646-87A5-647D3F4AC90B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD96B030-DC83-8C4B-8CAF-54863A79A7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="500" windowWidth="28000" windowHeight="16040" xr2:uid="{03A70420-2429-4913-AA09-83D42AAD96D5}"/>
   </bookViews>
@@ -5899,11 +5899,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6264,10 +6264,10 @@
       </c>
     </row>
     <row r="8" spans="2:203" x14ac:dyDescent="0.2">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="8"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="1" t="s">
         <v>1</v>
       </c>
@@ -7512,608 +7512,608 @@
       </c>
     </row>
     <row r="4" spans="2:203" x14ac:dyDescent="0.2">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="P4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="R4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="S4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="T4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="U4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="V4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="W4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="X4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="Y4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="Z4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AA4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AB4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AC4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AD4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AE4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AF4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AG4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AH4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AI4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AJ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AK4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AL4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AM4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AN4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AO4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AP4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AQ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AR4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AS4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AT4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AU4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AV4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AW4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AX4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AY4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AZ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BA4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BB4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BC4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BD4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BE4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BF4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BG4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BH4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BI4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BJ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BK4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BL4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BM4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BN4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BO4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BP4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BQ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BR4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BS4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BT4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BU4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BV4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BW4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BX4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BY4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="BZ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CA4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CB4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CC4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CD4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CE4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CF4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CG4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CH4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CI4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CJ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CK4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CL4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CM4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CN4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CO4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CP4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CQ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CR4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CS4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CT4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CU4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CV4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CW4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CX4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CY4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="CZ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DA4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DB4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DC4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DD4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DE4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DF4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DG4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DH4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DI4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DJ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DK4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DL4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DM4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DN4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DO4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DP4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DQ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DR4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DS4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DT4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DU4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DV4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DW4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DX4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DY4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DZ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EA4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EB4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EC4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="ED4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EE4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EF4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EG4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EH4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EI4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EJ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EK4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EL4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EM4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EN4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EO4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EP4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EQ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="ER4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="ES4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="ET4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EU4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EV4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EW4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EX4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EY4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="EZ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FA4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FB4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FC4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FD4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FE4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FF4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FG4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FH4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FI4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FJ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FK4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FL4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FM4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FN4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FO4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FP4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FQ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FR4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FS4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FT4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FU4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FV4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FW4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FX4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FY4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="FZ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GA4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GB4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GC4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GD4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GE4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GF4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GG4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GH4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GI4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GJ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GK4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GL4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GM4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GN4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GO4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GP4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GQ4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GR4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GS4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GT4" s="10" t="s">
-        <v>1895</v>
-      </c>
-      <c r="GU4" s="10" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AA4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AB4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AC4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AD4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AE4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AF4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AG4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AH4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AI4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AJ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AK4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AL4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AM4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AN4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AO4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AP4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AQ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AR4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AS4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AT4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AU4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AV4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AW4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AX4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AY4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AZ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BA4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BB4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BC4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BD4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BE4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BF4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BG4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BH4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BI4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BJ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BK4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BL4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BM4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BN4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BO4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BP4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BQ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BR4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BS4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BT4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BU4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BV4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BW4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BX4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BY4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="BZ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CA4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CB4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CC4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CD4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CE4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CF4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CG4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CH4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CI4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CJ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CK4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CL4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CM4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CN4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CO4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CP4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CQ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CR4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CS4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CT4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CU4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CV4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CW4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CX4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CY4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="CZ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DA4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DB4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DC4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DD4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DE4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DF4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DG4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DH4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DI4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DJ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DK4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DL4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DM4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DN4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DO4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DP4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DQ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DR4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DS4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DT4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DU4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DV4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DW4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DX4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DY4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DZ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EA4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EB4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EC4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="ED4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EE4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EF4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EG4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EH4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EI4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EJ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EK4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EL4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EM4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EN4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EO4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EP4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EQ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="ER4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="ES4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="ET4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EU4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EV4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EW4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EX4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EY4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="EZ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FA4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FB4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FC4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FD4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FE4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FF4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FG4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FH4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FI4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FJ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FK4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FL4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FM4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FN4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FO4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FP4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FQ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FR4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FS4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FT4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FU4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FV4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FW4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FX4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FY4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="FZ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GA4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GB4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GC4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GD4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GE4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GF4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GG4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GH4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GI4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GJ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GK4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GL4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GM4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GN4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GO4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GP4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GQ4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GR4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GS4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GT4" s="9" t="s">
+        <v>1895</v>
+      </c>
+      <c r="GU4" s="9" t="s">
         <v>1895</v>
       </c>
     </row>
@@ -8124,604 +8124,604 @@
       <c r="C5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>1896</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>1897</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>1898</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>1698</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>1699</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>1700</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>1701</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="8" t="s">
         <v>1702</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>1703</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="8" t="s">
         <v>1704</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="8" t="s">
         <v>1705</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O5" s="8" t="s">
         <v>1706</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="P5" s="8" t="s">
         <v>1707</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="Q5" s="8" t="s">
         <v>1708</v>
       </c>
-      <c r="R5" s="9" t="s">
+      <c r="R5" s="8" t="s">
         <v>1709</v>
       </c>
-      <c r="S5" s="9" t="s">
+      <c r="S5" s="8" t="s">
         <v>1710</v>
       </c>
-      <c r="T5" s="9" t="s">
+      <c r="T5" s="8" t="s">
         <v>1711</v>
       </c>
-      <c r="U5" s="9" t="s">
+      <c r="U5" s="8" t="s">
         <v>1712</v>
       </c>
-      <c r="V5" s="9" t="s">
+      <c r="V5" s="8" t="s">
         <v>1713</v>
       </c>
-      <c r="W5" s="9" t="s">
+      <c r="W5" s="8" t="s">
         <v>1714</v>
       </c>
-      <c r="X5" s="9" t="s">
+      <c r="X5" s="8" t="s">
         <v>1715</v>
       </c>
-      <c r="Y5" s="9" t="s">
+      <c r="Y5" s="8" t="s">
         <v>1716</v>
       </c>
-      <c r="Z5" s="9" t="s">
+      <c r="Z5" s="8" t="s">
         <v>1717</v>
       </c>
-      <c r="AA5" s="9" t="s">
+      <c r="AA5" s="8" t="s">
         <v>1718</v>
       </c>
-      <c r="AB5" s="9" t="s">
+      <c r="AB5" s="8" t="s">
         <v>1719</v>
       </c>
-      <c r="AC5" s="9" t="s">
+      <c r="AC5" s="8" t="s">
         <v>1720</v>
       </c>
-      <c r="AD5" s="9" t="s">
+      <c r="AD5" s="8" t="s">
         <v>1721</v>
       </c>
-      <c r="AE5" s="9" t="s">
+      <c r="AE5" s="8" t="s">
         <v>1722</v>
       </c>
-      <c r="AF5" s="9" t="s">
+      <c r="AF5" s="8" t="s">
         <v>1723</v>
       </c>
-      <c r="AG5" s="9" t="s">
+      <c r="AG5" s="8" t="s">
         <v>1724</v>
       </c>
-      <c r="AH5" s="9" t="s">
+      <c r="AH5" s="8" t="s">
         <v>1725</v>
       </c>
-      <c r="AI5" s="9" t="s">
+      <c r="AI5" s="8" t="s">
         <v>1726</v>
       </c>
-      <c r="AJ5" s="9" t="s">
+      <c r="AJ5" s="8" t="s">
         <v>1727</v>
       </c>
-      <c r="AK5" s="9" t="s">
+      <c r="AK5" s="8" t="s">
         <v>1728</v>
       </c>
-      <c r="AL5" s="9" t="s">
+      <c r="AL5" s="8" t="s">
         <v>1729</v>
       </c>
-      <c r="AM5" s="9" t="s">
+      <c r="AM5" s="8" t="s">
         <v>1730</v>
       </c>
-      <c r="AN5" s="9" t="s">
+      <c r="AN5" s="8" t="s">
         <v>1731</v>
       </c>
-      <c r="AO5" s="9" t="s">
+      <c r="AO5" s="8" t="s">
         <v>1732</v>
       </c>
-      <c r="AP5" s="9" t="s">
+      <c r="AP5" s="8" t="s">
         <v>1733</v>
       </c>
-      <c r="AQ5" s="9" t="s">
+      <c r="AQ5" s="8" t="s">
         <v>1734</v>
       </c>
-      <c r="AR5" s="9" t="s">
+      <c r="AR5" s="8" t="s">
         <v>1735</v>
       </c>
-      <c r="AS5" s="9" t="s">
+      <c r="AS5" s="8" t="s">
         <v>1736</v>
       </c>
-      <c r="AT5" s="9" t="s">
+      <c r="AT5" s="8" t="s">
         <v>1737</v>
       </c>
-      <c r="AU5" s="9" t="s">
+      <c r="AU5" s="8" t="s">
         <v>1738</v>
       </c>
-      <c r="AV5" s="9" t="s">
+      <c r="AV5" s="8" t="s">
         <v>1739</v>
       </c>
-      <c r="AW5" s="9" t="s">
+      <c r="AW5" s="8" t="s">
         <v>1740</v>
       </c>
-      <c r="AX5" s="9" t="s">
+      <c r="AX5" s="8" t="s">
         <v>1741</v>
       </c>
-      <c r="AY5" s="9" t="s">
+      <c r="AY5" s="8" t="s">
         <v>1742</v>
       </c>
-      <c r="AZ5" s="9" t="s">
+      <c r="AZ5" s="8" t="s">
         <v>1743</v>
       </c>
-      <c r="BA5" s="9" t="s">
+      <c r="BA5" s="8" t="s">
         <v>1744</v>
       </c>
-      <c r="BB5" s="9" t="s">
+      <c r="BB5" s="8" t="s">
         <v>1745</v>
       </c>
-      <c r="BC5" s="9" t="s">
+      <c r="BC5" s="8" t="s">
         <v>1746</v>
       </c>
-      <c r="BD5" s="9" t="s">
+      <c r="BD5" s="8" t="s">
         <v>1747</v>
       </c>
-      <c r="BE5" s="9" t="s">
+      <c r="BE5" s="8" t="s">
         <v>1748</v>
       </c>
-      <c r="BF5" s="9" t="s">
+      <c r="BF5" s="8" t="s">
         <v>1749</v>
       </c>
-      <c r="BG5" s="9" t="s">
+      <c r="BG5" s="8" t="s">
         <v>1750</v>
       </c>
-      <c r="BH5" s="9" t="s">
+      <c r="BH5" s="8" t="s">
         <v>1751</v>
       </c>
-      <c r="BI5" s="9" t="s">
+      <c r="BI5" s="8" t="s">
         <v>1752</v>
       </c>
-      <c r="BJ5" s="9" t="s">
+      <c r="BJ5" s="8" t="s">
         <v>1753</v>
       </c>
-      <c r="BK5" s="9" t="s">
+      <c r="BK5" s="8" t="s">
         <v>1754</v>
       </c>
-      <c r="BL5" s="9" t="s">
+      <c r="BL5" s="8" t="s">
         <v>1755</v>
       </c>
-      <c r="BM5" s="9" t="s">
+      <c r="BM5" s="8" t="s">
         <v>1756</v>
       </c>
-      <c r="BN5" s="9" t="s">
+      <c r="BN5" s="8" t="s">
         <v>1757</v>
       </c>
-      <c r="BO5" s="9" t="s">
+      <c r="BO5" s="8" t="s">
         <v>1758</v>
       </c>
-      <c r="BP5" s="9" t="s">
+      <c r="BP5" s="8" t="s">
         <v>1759</v>
       </c>
-      <c r="BQ5" s="9" t="s">
+      <c r="BQ5" s="8" t="s">
         <v>1760</v>
       </c>
-      <c r="BR5" s="9" t="s">
+      <c r="BR5" s="8" t="s">
         <v>1761</v>
       </c>
-      <c r="BS5" s="9" t="s">
+      <c r="BS5" s="8" t="s">
         <v>1762</v>
       </c>
-      <c r="BT5" s="9" t="s">
+      <c r="BT5" s="8" t="s">
         <v>1763</v>
       </c>
-      <c r="BU5" s="9" t="s">
+      <c r="BU5" s="8" t="s">
         <v>1764</v>
       </c>
-      <c r="BV5" s="9" t="s">
+      <c r="BV5" s="8" t="s">
         <v>1765</v>
       </c>
-      <c r="BW5" s="9" t="s">
+      <c r="BW5" s="8" t="s">
         <v>1766</v>
       </c>
-      <c r="BX5" s="9" t="s">
+      <c r="BX5" s="8" t="s">
         <v>1767</v>
       </c>
-      <c r="BY5" s="9" t="s">
+      <c r="BY5" s="8" t="s">
         <v>1768</v>
       </c>
-      <c r="BZ5" s="9" t="s">
+      <c r="BZ5" s="8" t="s">
         <v>1769</v>
       </c>
-      <c r="CA5" s="9" t="s">
+      <c r="CA5" s="8" t="s">
         <v>1770</v>
       </c>
-      <c r="CB5" s="9" t="s">
+      <c r="CB5" s="8" t="s">
         <v>1771</v>
       </c>
-      <c r="CC5" s="9" t="s">
+      <c r="CC5" s="8" t="s">
         <v>1772</v>
       </c>
-      <c r="CD5" s="9" t="s">
+      <c r="CD5" s="8" t="s">
         <v>1773</v>
       </c>
-      <c r="CE5" s="9" t="s">
+      <c r="CE5" s="8" t="s">
         <v>1774</v>
       </c>
-      <c r="CF5" s="9" t="s">
+      <c r="CF5" s="8" t="s">
         <v>1775</v>
       </c>
-      <c r="CG5" s="9" t="s">
+      <c r="CG5" s="8" t="s">
         <v>1776</v>
       </c>
-      <c r="CH5" s="9" t="s">
+      <c r="CH5" s="8" t="s">
         <v>1777</v>
       </c>
-      <c r="CI5" s="9" t="s">
+      <c r="CI5" s="8" t="s">
         <v>1778</v>
       </c>
-      <c r="CJ5" s="9" t="s">
+      <c r="CJ5" s="8" t="s">
         <v>1779</v>
       </c>
-      <c r="CK5" s="9" t="s">
+      <c r="CK5" s="8" t="s">
         <v>1780</v>
       </c>
-      <c r="CL5" s="9" t="s">
+      <c r="CL5" s="8" t="s">
         <v>1781</v>
       </c>
-      <c r="CM5" s="9" t="s">
+      <c r="CM5" s="8" t="s">
         <v>1782</v>
       </c>
-      <c r="CN5" s="9" t="s">
+      <c r="CN5" s="8" t="s">
         <v>1783</v>
       </c>
-      <c r="CO5" s="9" t="s">
+      <c r="CO5" s="8" t="s">
         <v>1784</v>
       </c>
-      <c r="CP5" s="9" t="s">
+      <c r="CP5" s="8" t="s">
         <v>1785</v>
       </c>
-      <c r="CQ5" s="9" t="s">
+      <c r="CQ5" s="8" t="s">
         <v>1786</v>
       </c>
-      <c r="CR5" s="9" t="s">
+      <c r="CR5" s="8" t="s">
         <v>1787</v>
       </c>
-      <c r="CS5" s="9" t="s">
+      <c r="CS5" s="8" t="s">
         <v>1788</v>
       </c>
-      <c r="CT5" s="9" t="s">
+      <c r="CT5" s="8" t="s">
         <v>1789</v>
       </c>
-      <c r="CU5" s="9" t="s">
+      <c r="CU5" s="8" t="s">
         <v>1790</v>
       </c>
-      <c r="CV5" s="9" t="s">
+      <c r="CV5" s="8" t="s">
         <v>1791</v>
       </c>
-      <c r="CW5" s="9" t="s">
+      <c r="CW5" s="8" t="s">
         <v>1792</v>
       </c>
-      <c r="CX5" s="9" t="s">
+      <c r="CX5" s="8" t="s">
         <v>1793</v>
       </c>
-      <c r="CY5" s="9" t="s">
+      <c r="CY5" s="8" t="s">
         <v>1794</v>
       </c>
-      <c r="CZ5" s="9" t="s">
+      <c r="CZ5" s="8" t="s">
         <v>1795</v>
       </c>
-      <c r="DA5" s="9" t="s">
+      <c r="DA5" s="8" t="s">
         <v>1796</v>
       </c>
-      <c r="DB5" s="9" t="s">
+      <c r="DB5" s="8" t="s">
         <v>1797</v>
       </c>
-      <c r="DC5" s="9" t="s">
+      <c r="DC5" s="8" t="s">
         <v>1798</v>
       </c>
-      <c r="DD5" s="9" t="s">
+      <c r="DD5" s="8" t="s">
         <v>1799</v>
       </c>
-      <c r="DE5" s="9" t="s">
+      <c r="DE5" s="8" t="s">
         <v>1800</v>
       </c>
-      <c r="DF5" s="9" t="s">
+      <c r="DF5" s="8" t="s">
         <v>1801</v>
       </c>
-      <c r="DG5" s="9" t="s">
+      <c r="DG5" s="8" t="s">
         <v>1802</v>
       </c>
-      <c r="DH5" s="9" t="s">
+      <c r="DH5" s="8" t="s">
         <v>1803</v>
       </c>
-      <c r="DI5" s="9" t="s">
+      <c r="DI5" s="8" t="s">
         <v>1804</v>
       </c>
-      <c r="DJ5" s="9" t="s">
+      <c r="DJ5" s="8" t="s">
         <v>1805</v>
       </c>
-      <c r="DK5" s="9" t="s">
+      <c r="DK5" s="8" t="s">
         <v>1806</v>
       </c>
-      <c r="DL5" s="9" t="s">
+      <c r="DL5" s="8" t="s">
         <v>1807</v>
       </c>
-      <c r="DM5" s="9" t="s">
+      <c r="DM5" s="8" t="s">
         <v>1808</v>
       </c>
-      <c r="DN5" s="9" t="s">
+      <c r="DN5" s="8" t="s">
         <v>1809</v>
       </c>
-      <c r="DO5" s="9" t="s">
+      <c r="DO5" s="8" t="s">
         <v>1810</v>
       </c>
-      <c r="DP5" s="9" t="s">
+      <c r="DP5" s="8" t="s">
         <v>1811</v>
       </c>
-      <c r="DQ5" s="9" t="s">
+      <c r="DQ5" s="8" t="s">
         <v>1812</v>
       </c>
-      <c r="DR5" s="9" t="s">
+      <c r="DR5" s="8" t="s">
         <v>1813</v>
       </c>
-      <c r="DS5" s="9" t="s">
+      <c r="DS5" s="8" t="s">
         <v>1814</v>
       </c>
-      <c r="DT5" s="9" t="s">
+      <c r="DT5" s="8" t="s">
         <v>1815</v>
       </c>
-      <c r="DU5" s="9" t="s">
+      <c r="DU5" s="8" t="s">
         <v>1816</v>
       </c>
-      <c r="DV5" s="9" t="s">
+      <c r="DV5" s="8" t="s">
         <v>1817</v>
       </c>
-      <c r="DW5" s="9" t="s">
+      <c r="DW5" s="8" t="s">
         <v>1818</v>
       </c>
-      <c r="DX5" s="9" t="s">
+      <c r="DX5" s="8" t="s">
         <v>1819</v>
       </c>
-      <c r="DY5" s="9" t="s">
+      <c r="DY5" s="8" t="s">
         <v>1820</v>
       </c>
-      <c r="DZ5" s="9" t="s">
+      <c r="DZ5" s="8" t="s">
         <v>1821</v>
       </c>
-      <c r="EA5" s="9" t="s">
+      <c r="EA5" s="8" t="s">
         <v>1822</v>
       </c>
-      <c r="EB5" s="9" t="s">
+      <c r="EB5" s="8" t="s">
         <v>1823</v>
       </c>
-      <c r="EC5" s="9" t="s">
+      <c r="EC5" s="8" t="s">
         <v>1824</v>
       </c>
-      <c r="ED5" s="9" t="s">
+      <c r="ED5" s="8" t="s">
         <v>1825</v>
       </c>
-      <c r="EE5" s="9" t="s">
+      <c r="EE5" s="8" t="s">
         <v>1826</v>
       </c>
-      <c r="EF5" s="9" t="s">
+      <c r="EF5" s="8" t="s">
         <v>1827</v>
       </c>
-      <c r="EG5" s="9" t="s">
+      <c r="EG5" s="8" t="s">
         <v>1828</v>
       </c>
-      <c r="EH5" s="9" t="s">
+      <c r="EH5" s="8" t="s">
         <v>1829</v>
       </c>
-      <c r="EI5" s="9" t="s">
+      <c r="EI5" s="8" t="s">
         <v>1830</v>
       </c>
-      <c r="EJ5" s="9" t="s">
+      <c r="EJ5" s="8" t="s">
         <v>1831</v>
       </c>
-      <c r="EK5" s="9" t="s">
+      <c r="EK5" s="8" t="s">
         <v>1832</v>
       </c>
-      <c r="EL5" s="9" t="s">
+      <c r="EL5" s="8" t="s">
         <v>1833</v>
       </c>
-      <c r="EM5" s="9" t="s">
+      <c r="EM5" s="8" t="s">
         <v>1834</v>
       </c>
-      <c r="EN5" s="9" t="s">
+      <c r="EN5" s="8" t="s">
         <v>1835</v>
       </c>
-      <c r="EO5" s="9" t="s">
+      <c r="EO5" s="8" t="s">
         <v>1836</v>
       </c>
-      <c r="EP5" s="9" t="s">
+      <c r="EP5" s="8" t="s">
         <v>1837</v>
       </c>
-      <c r="EQ5" s="9" t="s">
+      <c r="EQ5" s="8" t="s">
         <v>1838</v>
       </c>
-      <c r="ER5" s="9" t="s">
+      <c r="ER5" s="8" t="s">
         <v>1839</v>
       </c>
-      <c r="ES5" s="9" t="s">
+      <c r="ES5" s="8" t="s">
         <v>1840</v>
       </c>
-      <c r="ET5" s="9" t="s">
+      <c r="ET5" s="8" t="s">
         <v>1841</v>
       </c>
-      <c r="EU5" s="9" t="s">
+      <c r="EU5" s="8" t="s">
         <v>1842</v>
       </c>
-      <c r="EV5" s="9" t="s">
+      <c r="EV5" s="8" t="s">
         <v>1843</v>
       </c>
-      <c r="EW5" s="9" t="s">
+      <c r="EW5" s="8" t="s">
         <v>1844</v>
       </c>
-      <c r="EX5" s="9" t="s">
+      <c r="EX5" s="8" t="s">
         <v>1845</v>
       </c>
-      <c r="EY5" s="9" t="s">
+      <c r="EY5" s="8" t="s">
         <v>1846</v>
       </c>
-      <c r="EZ5" s="9" t="s">
+      <c r="EZ5" s="8" t="s">
         <v>1847</v>
       </c>
-      <c r="FA5" s="9" t="s">
+      <c r="FA5" s="8" t="s">
         <v>1848</v>
       </c>
-      <c r="FB5" s="9" t="s">
+      <c r="FB5" s="8" t="s">
         <v>1849</v>
       </c>
-      <c r="FC5" s="9" t="s">
+      <c r="FC5" s="8" t="s">
         <v>1850</v>
       </c>
-      <c r="FD5" s="9" t="s">
+      <c r="FD5" s="8" t="s">
         <v>1851</v>
       </c>
-      <c r="FE5" s="9" t="s">
+      <c r="FE5" s="8" t="s">
         <v>1852</v>
       </c>
-      <c r="FF5" s="9" t="s">
+      <c r="FF5" s="8" t="s">
         <v>1853</v>
       </c>
-      <c r="FG5" s="9" t="s">
+      <c r="FG5" s="8" t="s">
         <v>1854</v>
       </c>
-      <c r="FH5" s="9" t="s">
+      <c r="FH5" s="8" t="s">
         <v>1855</v>
       </c>
-      <c r="FI5" s="9" t="s">
+      <c r="FI5" s="8" t="s">
         <v>1856</v>
       </c>
-      <c r="FJ5" s="9" t="s">
+      <c r="FJ5" s="8" t="s">
         <v>1857</v>
       </c>
-      <c r="FK5" s="9" t="s">
+      <c r="FK5" s="8" t="s">
         <v>1858</v>
       </c>
-      <c r="FL5" s="9" t="s">
+      <c r="FL5" s="8" t="s">
         <v>1859</v>
       </c>
-      <c r="FM5" s="9" t="s">
+      <c r="FM5" s="8" t="s">
         <v>1860</v>
       </c>
-      <c r="FN5" s="9" t="s">
+      <c r="FN5" s="8" t="s">
         <v>1861</v>
       </c>
-      <c r="FO5" s="9" t="s">
+      <c r="FO5" s="8" t="s">
         <v>1862</v>
       </c>
-      <c r="FP5" s="9" t="s">
+      <c r="FP5" s="8" t="s">
         <v>1863</v>
       </c>
-      <c r="FQ5" s="9" t="s">
+      <c r="FQ5" s="8" t="s">
         <v>1864</v>
       </c>
-      <c r="FR5" s="9" t="s">
+      <c r="FR5" s="8" t="s">
         <v>1865</v>
       </c>
-      <c r="FS5" s="9" t="s">
+      <c r="FS5" s="8" t="s">
         <v>1866</v>
       </c>
-      <c r="FT5" s="9" t="s">
+      <c r="FT5" s="8" t="s">
         <v>1867</v>
       </c>
-      <c r="FU5" s="9" t="s">
+      <c r="FU5" s="8" t="s">
         <v>1868</v>
       </c>
-      <c r="FV5" s="9" t="s">
+      <c r="FV5" s="8" t="s">
         <v>1869</v>
       </c>
-      <c r="FW5" s="9" t="s">
+      <c r="FW5" s="8" t="s">
         <v>1870</v>
       </c>
-      <c r="FX5" s="9" t="s">
+      <c r="FX5" s="8" t="s">
         <v>1871</v>
       </c>
-      <c r="FY5" s="9" t="s">
+      <c r="FY5" s="8" t="s">
         <v>1872</v>
       </c>
-      <c r="FZ5" s="9" t="s">
+      <c r="FZ5" s="8" t="s">
         <v>1873</v>
       </c>
-      <c r="GA5" s="9" t="s">
+      <c r="GA5" s="8" t="s">
         <v>1874</v>
       </c>
-      <c r="GB5" s="9" t="s">
+      <c r="GB5" s="8" t="s">
         <v>1875</v>
       </c>
-      <c r="GC5" s="9" t="s">
+      <c r="GC5" s="8" t="s">
         <v>1876</v>
       </c>
-      <c r="GD5" s="9" t="s">
+      <c r="GD5" s="8" t="s">
         <v>1877</v>
       </c>
-      <c r="GE5" s="9" t="s">
+      <c r="GE5" s="8" t="s">
         <v>1878</v>
       </c>
-      <c r="GF5" s="9" t="s">
+      <c r="GF5" s="8" t="s">
         <v>1879</v>
       </c>
-      <c r="GG5" s="9" t="s">
+      <c r="GG5" s="8" t="s">
         <v>1880</v>
       </c>
-      <c r="GH5" s="9" t="s">
+      <c r="GH5" s="8" t="s">
         <v>1881</v>
       </c>
-      <c r="GI5" s="9" t="s">
+      <c r="GI5" s="8" t="s">
         <v>1882</v>
       </c>
-      <c r="GJ5" s="9" t="s">
+      <c r="GJ5" s="8" t="s">
         <v>1883</v>
       </c>
-      <c r="GK5" s="9" t="s">
+      <c r="GK5" s="8" t="s">
         <v>1884</v>
       </c>
-      <c r="GL5" s="9" t="s">
+      <c r="GL5" s="8" t="s">
         <v>1885</v>
       </c>
-      <c r="GM5" s="9" t="s">
+      <c r="GM5" s="8" t="s">
         <v>1886</v>
       </c>
-      <c r="GN5" s="9" t="s">
+      <c r="GN5" s="8" t="s">
         <v>1887</v>
       </c>
-      <c r="GO5" s="9" t="s">
+      <c r="GO5" s="8" t="s">
         <v>1888</v>
       </c>
-      <c r="GP5" s="9" t="s">
+      <c r="GP5" s="8" t="s">
         <v>1889</v>
       </c>
-      <c r="GQ5" s="9" t="s">
+      <c r="GQ5" s="8" t="s">
         <v>1890</v>
       </c>
-      <c r="GR5" s="9" t="s">
+      <c r="GR5" s="8" t="s">
         <v>1891</v>
       </c>
-      <c r="GS5" s="9" t="s">
+      <c r="GS5" s="8" t="s">
         <v>1892</v>
       </c>
-      <c r="GT5" s="9" t="s">
+      <c r="GT5" s="8" t="s">
         <v>1893</v>
       </c>
-      <c r="GU5" s="9" t="s">
+      <c r="GU5" s="8" t="s">
         <v>1894</v>
       </c>
     </row>
@@ -15576,6 +15576,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f8fd78c8-cd58-4647-bdeb-fdcf2106eb82">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c343035a-eeff-4647-bb36-aa636a1a9180" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009FDD8E3FE5876F4E813B2FAE82B41E03" ma:contentTypeVersion="16" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="cb12b29134862a5551f6c1afe8cc1c27">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f8fd78c8-cd58-4647-bdeb-fdcf2106eb82" xmlns:ns3="c343035a-eeff-4647-bb36-aa636a1a9180" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a7f20c03ce02b47dd9895f5ff8ceaf6c" ns2:_="" ns3:_="">
     <xsd:import namespace="f8fd78c8-cd58-4647-bdeb-fdcf2106eb82"/>
@@ -15810,41 +15830,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f8fd78c8-cd58-4647-bdeb-fdcf2106eb82">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c343035a-eeff-4647-bb36-aa636a1a9180" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CE0C152-A899-40D5-9FD0-0940F8D80769}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8885907-55A8-461B-8EC8-E298CEBCC84E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f8fd78c8-cd58-4647-bdeb-fdcf2106eb82"/>
-    <ds:schemaRef ds:uri="c343035a-eeff-4647-bb36-aa636a1a9180"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15867,9 +15856,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8885907-55A8-461B-8EC8-E298CEBCC84E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CE0C152-A899-40D5-9FD0-0940F8D80769}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f8fd78c8-cd58-4647-bdeb-fdcf2106eb82"/>
+    <ds:schemaRef ds:uri="c343035a-eeff-4647-bb36-aa636a1a9180"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>